--- a/deliverables/ITles_Fuchs_telematics.xlsx
+++ b/deliverables/ITles_Fuchs_telematics.xlsx
@@ -8959,7 +8959,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Официальные поставки в РФ прекращены в 2022: не закладывать</t>
+          <t>Официальные поставки в РФ прекращены в 2022 (есть серый импорт — без официальной поддержки и прошивок): не закладывать</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
